--- a/public/catalogue/modele_boutique.xlsx
+++ b/public/catalogue/modele_boutique.xlsx
@@ -7,9 +7,6 @@
     <sheet name="modele_boutique" sheetId="2" r:id="rId2"/>
     <sheet name="VALEURS" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'modele_boutique'!A1:AG26</definedName>
-  </definedNames>
 </workbook>
 </file>
 
@@ -402,10 +399,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B71"/>
+  <dimension ref="A1:B14"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="110.83203125" customWidth="1"/>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="88.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -423,7 +420,7 @@
         <v>Règle d’or</v>
       </c>
       <c r="B3" t="str">
-        <v>Cellule vide = non. Rien n’est inventé (pas de panneau, pas de tablette, pas d’option).</v>
+        <v>Cellule vide = non. Rien n’est inventé.</v>
       </c>
     </row>
     <row r="4">
@@ -431,498 +428,90 @@
         <v>Unité</v>
       </c>
       <c r="B4" t="str">
-        <v>Millimètres entiers. L / P / H entre 200 et 2200.</v>
+        <v>Millimètres. L / P / H entre 200 et 2200.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>P</v>
+        <v>DAE / GLB</v>
       </c>
       <c r="B5" t="str">
-        <v>Profondeur du meuble (axe Y). Dans le 3D c’est W.</v>
+        <v>Ne pas joindre. Le 3D est reconstruit depuis cette feuille.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Section d’arête</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Calculée toute seule : max(L,P,H) &lt; 1000 → 30×30 ; sinon 40×40. Ne pas la saisir.</v>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Épaisseurs</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Panneau et porte figés à 15 mm. Ne pas les saisir.</v>
+        <v>5 premières configs (201–205)</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Prix</v>
+        <v>201</v>
       </c>
       <c r="B8" t="str">
-        <v>Recalculé par le site à partir de L/P/H + panneaux + modules. Ne pas le saisir.</v>
+        <v>Bar cuisine — saisie atelier (joue1 + dessus, tablettes 400|700)</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>DAE / GLB</v>
+        <v>202</v>
       </c>
       <c r="B9" t="str">
-        <v>Ne pas joindre. Le 3D est reconstruit depuis cette feuille. Le DAE reste un export d’atelier local.</v>
+        <v>Chevet — 1 tiroir 84 + 1 tablette + dessus</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v/>
+        <v>203</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Commode — 2 tiroirs 136 + 1 tablette + socle + dessus</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>COLONNES OBLIGATOIRES POUR QU’UN MODÈLE EXISTE</v>
+        <v>204</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Bibliothèque — 5 tablettes calées + fond/socle/dessus</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Boutique</v>
+        <v>205</v>
       </c>
       <c r="B12" t="str">
-        <v>O = visible en boutique. Vide = masqué (ligne conservée pour plus tard).</v>
+        <v>Dressing — porte double, joues, tiroirs 188|214, 4 tablettes</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Numéro unique stable (101, 102…). Sert à l’URL, au SKU et au fichier d’aperçu. Ne plus le changer ensuite.</v>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Piece / Room</v>
+        <v>Livraison</v>
       </c>
       <c r="B14" t="str">
-        <v>Catégorie FR / EN (Chambre / Bedroom, Salon / Living room…).</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Nom / Name</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Nom FR / EN de la fiche.</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>L P H</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Enveloppe figée côté client. Il pourra changer tablettes, tiroirs, panneaux, couleur — pas L×P×H.</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>APPARENCE</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>couleur_ossature</v>
-      </c>
-      <c r="B19" t="str">
-        <v>brut  |  vernis_clair     (finition de surface. L’essence bois est atelier, pas client.)</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>couleur_panneau</v>
-      </c>
-      <c r="B20" t="str">
-        <v>Défaut parmi : terracotta | olive | bleu_poudre | gris_cendre | jaune_orange | noir_mat</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>porte_charniere</v>
-      </c>
-      <c r="B21" t="str">
-        <v>left (gauche) | right (droite) | center (double / milieu). Vide = auto selon L.</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v/>
-      </c>
-      <c r="B22" t="str">
-        <v>Contrainte porte : L &lt; 400 → pas de double ; L &gt; 600 → double obligatoire ; L &gt; 1200 → pas de porte.</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>PANNEAUX (O = présent au départ, vide = absent)</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>porte</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Façade avant (Y max).</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>fond</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Dos (Y min).</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>joue1</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Joue gauche (X min).</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>joue2</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Joue droite (X max).</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>socle</v>
-      </c>
-      <c r="B29" t="str">
-        <v>Dessous / plancher.</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>dessus</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Dessus extérieur (plafond du meuble).</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>dessus_int</v>
-      </c>
-      <c r="B31" t="str">
-        <v>Dessus intérieur (option rare).</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>TABLETTES</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v># tablette</v>
-      </c>
-      <c r="B34" t="str">
-        <v>Nombre de tablettes au départ. 0 ou vide = aucune.</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>tablettes_z</v>
-      </c>
-      <c r="B35" t="str">
-        <v>Optionnel. Haut de chaque octogone en mm, du bas vers le haut, séparés par |</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v/>
-      </c>
-      <c r="B36" t="str">
-        <v>Exemple : 400|700|1000|1300|1600</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v/>
-      </c>
-      <c r="B37" t="str">
-        <v>Vide = répartition automatique dans la hauteur utile.</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v/>
-      </c>
-      <c r="B38" t="str">
-        <v>S’il y a des tiroirs, la 1re tablette est calée sur le dessus des tiroirs (fermeture). Les Z suivants = tablettes au-dessus.</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>TIROIRS</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v># tiroir</v>
-      </c>
-      <c r="B41" t="str">
-        <v>Nombre de tiroirs au départ. 0 ou vide = aucun.</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>hauteur_tiroir</v>
-      </c>
-      <c r="B42" t="str">
-        <v>Hauteur Würth unique si tous les tiroirs sont identiques.</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>tiroirs_h</v>
-      </c>
-      <c r="B43" t="str">
-        <v>Optionnel. Une hauteur par tiroir, du bas vers le haut, séparées par |  Ex. 84|136</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v/>
-      </c>
-      <c r="B44" t="str">
-        <v>Hauteurs Würth ASTUCIO type B (mm) : 58 | 84 | 110 | 136 | 162 | 188 | 214 | 240 | 266</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v/>
-      </c>
-      <c r="B45" t="str">
-        <v>Toute autre valeur est ramenée à la plus proche de cette liste.</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v/>
-      </c>
-      <c r="B46" t="str">
-        <v>Le Z des tiroirs n’est PAS saisissable : empilement automatique depuis le sol (jeu 15 mm).</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v/>
-      </c>
-      <c r="B47" t="str">
-        <v>Profondeur mini tiroir : 250 mm (P du meuble). Largeur intérieure utile : 200–1200 mm.</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>CASES (optionnel — panneaux partiels)</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v/>
-      </c>
-      <c r="B50" t="str">
-        <v>Les tablettes et tiroirs découpent le meuble en cases verticales, du bas (0) vers le haut.</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v/>
-      </c>
-      <c r="B51" t="str">
-        <v>Vide = toute la face si le O correspondant est coché.</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>porte_cases</v>
-      </c>
-      <c r="B52" t="str">
-        <v>Ex. 1|2 = porte seulement sur les cases 1 et 2 (pas sur le bas).</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>fond_cases</v>
-      </c>
-      <c r="B53" t="str">
-        <v>Idem pour le fond.</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v>joue1_cases / joue2_cases</v>
-      </c>
-      <c r="B54" t="str">
-        <v>Idem pour les joues. Les cases imposées par une porte ne sont pas retirables.</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v>META</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v>MiseEnAvant</v>
-      </c>
-      <c r="B57" t="str">
-        <v>O = mis en avant sur la grille boutique.</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v>tags</v>
-      </c>
-      <c r="B58" t="str">
-        <v>Mots-clés séparés par espace ou virgule (chevet chambre).</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v>Options</v>
-      </c>
-      <c r="B59" t="str">
-        <v>Notes atelier (non lues par le 3D).</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>Description FR / ENG</v>
-      </c>
-      <c r="B60" t="str">
-        <v>Textes fiche produit.</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>CE QUE LE CLIENT POURRA ENCORE CHANGER (configurateur boutique)</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v/>
-      </c>
-      <c r="B63" t="str">
-        <v>Couleur parmi les 6 · nombre et position des tablettes · nombre et hauteur des tiroirs · ajouter/enlever panneaux et portes.</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v/>
-      </c>
-      <c r="B64" t="str">
-        <v>Il ne pourra PAS changer L, P, H sur la fiche boutique (configurateur libre = autre parcours).</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v>FEUILLES DE CE CLASSEUR</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="str">
-        <v>LEGENDE</v>
-      </c>
-      <c r="B67" t="str">
-        <v>Ceci.</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v>modele_boutique</v>
-      </c>
-      <c r="B68" t="str">
-        <v>À REMPLIR. Les 3 premières lignes sont des EXEMPLES : supprimez-les avant livraison.</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>VALEURS</v>
-      </c>
-      <c r="B69" t="str">
-        <v>Listes autorisées (à copier-coller).</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v>Livraison</v>
-      </c>
-      <c r="B71" t="str">
-        <v>Renvoyez ce .xlsx rempli (ou le .csv). Pas de DAE.</v>
+        <v>Compléter 206+ ou corriger 201–205. Pas de DAE.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B71"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B14"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AG26"/>
+  <dimension ref="A1:AG23"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -1065,37 +654,37 @@
         <v>O</v>
       </c>
       <c r="B2" t="str">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="C2" t="str">
-        <v>Chambre</v>
+        <v>Cuisine</v>
       </c>
       <c r="D2" t="str">
-        <v>Bedroom</v>
+        <v>Kitchen</v>
       </c>
       <c r="E2" t="str">
-        <v>Table Chevet</v>
+        <v>Bar</v>
       </c>
       <c r="F2" t="str">
-        <v>Bedside table</v>
+        <v>Bar</v>
       </c>
       <c r="G2">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H2">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="I2">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="J2" t="str">
-        <v>Chevet 1 tiroir, 1 tablette — EXEMPLE à supprimer</v>
+        <v>Bar 40 × 60 × 90 cm, deux tablettes. Une joue et un dessus.</v>
       </c>
       <c r="K2" t="str">
-        <v>Bedside 1 drawer, 1 shelf — SAMPLE, delete me</v>
+        <v>Bar 40 × 60 × 90 cm, two shelves. One side panel and a top.</v>
       </c>
       <c r="L2" t="str">
-        <v>chevet chambre</v>
+        <v>bar cuisine</v>
       </c>
       <c r="M2" t="str">
         <v>brut</v>
@@ -1113,34 +702,34 @@
         <v/>
       </c>
       <c r="R2" t="str">
-        <v/>
+        <v>O</v>
       </c>
       <c r="S2" t="str">
         <v/>
       </c>
       <c r="T2" t="str">
-        <v>O</v>
+        <v/>
       </c>
       <c r="U2" t="str">
-        <v/>
+        <v>O</v>
       </c>
       <c r="V2" t="str">
         <v/>
       </c>
       <c r="W2">
-        <v>1</v>
-      </c>
-      <c r="X2">
-        <v>84</v>
+        <v>0</v>
+      </c>
+      <c r="X2" t="str">
+        <v/>
       </c>
       <c r="Y2" t="str">
         <v/>
       </c>
       <c r="Z2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA2" t="str">
-        <v/>
+        <v>400|700</v>
       </c>
       <c r="AB2" t="str">
         <v/>
@@ -1158,7 +747,7 @@
         <v>O</v>
       </c>
       <c r="AG2" t="str">
-        <v>EXEMPLE — tablettes_z vide = répartition auto</v>
+        <v>Saisie atelier — joue gauche + dessus, tablettes à 400 et 700 mm</v>
       </c>
     </row>
     <row r="3">
@@ -1166,43 +755,43 @@
         <v>O</v>
       </c>
       <c r="B3" t="str">
-        <v>102</v>
+        <v>202</v>
       </c>
       <c r="C3" t="str">
-        <v>Couloir / entrée</v>
+        <v>Chambre</v>
       </c>
       <c r="D3" t="str">
-        <v>Hall / entry</v>
+        <v>Bedroom</v>
       </c>
       <c r="E3" t="str">
-        <v>Bibliothèque</v>
+        <v>Table Chevet</v>
       </c>
       <c r="F3" t="str">
-        <v>Bookcase</v>
+        <v>Bedside table</v>
       </c>
       <c r="G3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I3">
-        <v>1800</v>
+        <v>500</v>
       </c>
       <c r="J3" t="str">
-        <v>Colonne 5 tablettes calées — EXEMPLE à supprimer</v>
+        <v>Chevet 30 × 30 × 50 cm, un tiroir 84 mm et une tablette.</v>
       </c>
       <c r="K3" t="str">
-        <v>Column 5 placed shelves — SAMPLE, delete me</v>
+        <v>Bedside 30 × 30 × 50 cm, one 84 mm drawer and one shelf.</v>
       </c>
       <c r="L3" t="str">
-        <v>bibliotheque</v>
+        <v>chevet chambre</v>
       </c>
       <c r="M3" t="str">
         <v>brut</v>
       </c>
       <c r="N3" t="str">
-        <v>bleu_poudre</v>
+        <v>olive</v>
       </c>
       <c r="O3" t="str">
         <v/>
@@ -1211,7 +800,7 @@
         <v/>
       </c>
       <c r="Q3" t="str">
-        <v>O</v>
+        <v/>
       </c>
       <c r="R3" t="str">
         <v/>
@@ -1220,7 +809,7 @@
         <v/>
       </c>
       <c r="T3" t="str">
-        <v>O</v>
+        <v/>
       </c>
       <c r="U3" t="str">
         <v>O</v>
@@ -1229,19 +818,19 @@
         <v/>
       </c>
       <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3" t="str">
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="X3">
+        <v>84</v>
       </c>
       <c r="Y3" t="str">
         <v/>
       </c>
       <c r="Z3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="str">
-        <v>400|700|1000|1300|1600</v>
+        <v/>
       </c>
       <c r="AB3" t="str">
         <v/>
@@ -1256,10 +845,10 @@
         <v/>
       </c>
       <c r="AF3" t="str">
-        <v/>
+        <v>O</v>
       </c>
       <c r="AG3" t="str">
-        <v>EXEMPLE — tablettes_z = haut de chaque octogone (mm)</v>
+        <v>1re tablette calée sur le tiroir (fermeture)</v>
       </c>
     </row>
     <row r="4">
@@ -1267,7 +856,7 @@
         <v>O</v>
       </c>
       <c r="B4" t="str">
-        <v>103</v>
+        <v>203</v>
       </c>
       <c r="C4" t="str">
         <v>Chambre</v>
@@ -1276,55 +865,55 @@
         <v>Bedroom</v>
       </c>
       <c r="E4" t="str">
-        <v>Dressing</v>
+        <v>Commode</v>
       </c>
       <c r="F4" t="str">
-        <v>Wardrobe</v>
+        <v>Chest of drawers</v>
       </c>
       <c r="G4">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="H4">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="I4">
-        <v>1900</v>
+        <v>850</v>
       </c>
       <c r="J4" t="str">
-        <v>Dressing 2 tiroirs + porte double — EXEMPLE à supprimer</v>
+        <v>Commode 60 × 40 × 85 cm, deux tiroirs 136 mm, une tablette, socle et dessus.</v>
       </c>
       <c r="K4" t="str">
-        <v>Wardrobe 2 drawers + double door — SAMPLE, delete me</v>
+        <v>Chest 60 × 40 × 85 cm, two 136 mm drawers, one shelf, plinth and top.</v>
       </c>
       <c r="L4" t="str">
-        <v>dressing chambre</v>
+        <v>commode chambre</v>
       </c>
       <c r="M4" t="str">
-        <v>vernis_clair</v>
+        <v>brut</v>
       </c>
       <c r="N4" t="str">
         <v>terracotta</v>
       </c>
       <c r="O4" t="str">
-        <v>center</v>
+        <v/>
       </c>
       <c r="P4" t="str">
-        <v>O</v>
+        <v/>
       </c>
       <c r="Q4" t="str">
         <v/>
       </c>
       <c r="R4" t="str">
-        <v>O</v>
+        <v/>
       </c>
       <c r="S4" t="str">
-        <v>O</v>
+        <v/>
       </c>
       <c r="T4" t="str">
-        <v/>
+        <v>O</v>
       </c>
       <c r="U4" t="str">
-        <v/>
+        <v>O</v>
       </c>
       <c r="V4" t="str">
         <v/>
@@ -1333,13 +922,13 @@
         <v>2</v>
       </c>
       <c r="X4">
-        <v>214</v>
+        <v>136</v>
       </c>
       <c r="Y4" t="str">
-        <v>188|214</v>
+        <v/>
       </c>
       <c r="Z4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="str">
         <v/>
@@ -1360,7 +949,7 @@
         <v/>
       </c>
       <c r="AG4" t="str">
-        <v>EXEMPLE — L&gt;600 mm ⇒ charnière center obligatoire</v>
+        <v>Tiroirs identiques 136 mm, empilement auto</v>
       </c>
     </row>
     <row r="5">
@@ -1368,43 +957,43 @@
         <v>O</v>
       </c>
       <c r="B5" t="str">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>Couloir / entrée</v>
       </c>
       <c r="D5" t="str">
-        <v/>
+        <v>Hall / entry</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>Bibliothèque</v>
       </c>
       <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v/>
+        <v>Bookcase</v>
+      </c>
+      <c r="G5">
+        <v>400</v>
+      </c>
+      <c r="H5">
+        <v>400</v>
+      </c>
+      <c r="I5">
+        <v>1800</v>
       </c>
       <c r="J5" t="str">
-        <v/>
+        <v>Colonne 40 × 40 × 180 cm, cinq tablettes calées, fond, socle et dessus.</v>
       </c>
       <c r="K5" t="str">
-        <v/>
+        <v>Column 40 × 40 × 180 cm, five placed shelves, back, plinth and top.</v>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>bibliotheque entree</v>
       </c>
       <c r="M5" t="str">
         <v>brut</v>
       </c>
       <c r="N5" t="str">
-        <v>olive</v>
+        <v>bleu_poudre</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -1413,7 +1002,7 @@
         <v/>
       </c>
       <c r="Q5" t="str">
-        <v/>
+        <v>O</v>
       </c>
       <c r="R5" t="str">
         <v/>
@@ -1422,16 +1011,16 @@
         <v/>
       </c>
       <c r="T5" t="str">
-        <v/>
+        <v>O</v>
       </c>
       <c r="U5" t="str">
-        <v/>
+        <v>O</v>
       </c>
       <c r="V5" t="str">
         <v/>
       </c>
-      <c r="W5" t="str">
-        <v/>
+      <c r="W5">
+        <v>0</v>
       </c>
       <c r="X5" t="str">
         <v/>
@@ -1439,11 +1028,11 @@
       <c r="Y5" t="str">
         <v/>
       </c>
-      <c r="Z5" t="str">
-        <v/>
+      <c r="Z5">
+        <v>5</v>
       </c>
       <c r="AA5" t="str">
-        <v/>
+        <v>400|700|1000|1300|1600</v>
       </c>
       <c r="AB5" t="str">
         <v/>
@@ -1458,10 +1047,10 @@
         <v/>
       </c>
       <c r="AF5" t="str">
-        <v/>
+        <v>O</v>
       </c>
       <c r="AG5" t="str">
-        <v/>
+        <v>tablettes_z = haut d’octogone (mm), bas → haut</v>
       </c>
     </row>
     <row r="6">
@@ -1469,58 +1058,58 @@
         <v>O</v>
       </c>
       <c r="B6" t="str">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>Chambre</v>
       </c>
       <c r="D6" t="str">
-        <v/>
+        <v>Bedroom</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>Dressing</v>
       </c>
       <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v/>
+        <v>Wardrobe</v>
+      </c>
+      <c r="G6">
+        <v>800</v>
+      </c>
+      <c r="H6">
+        <v>450</v>
+      </c>
+      <c r="I6">
+        <v>1900</v>
       </c>
       <c r="J6" t="str">
-        <v/>
+        <v>Dressing 80 × 45 × 190 cm, deux tiroirs, quatre tablettes, porte double et joues.</v>
       </c>
       <c r="K6" t="str">
-        <v/>
+        <v>Wardrobe 80 × 45 × 190 cm, two drawers, four shelves, double door and sides.</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>dressing chambre</v>
       </c>
       <c r="M6" t="str">
-        <v>brut</v>
+        <v>vernis_clair</v>
       </c>
       <c r="N6" t="str">
-        <v>olive</v>
+        <v>terracotta</v>
       </c>
       <c r="O6" t="str">
-        <v/>
+        <v>center</v>
       </c>
       <c r="P6" t="str">
-        <v/>
+        <v>O</v>
       </c>
       <c r="Q6" t="str">
         <v/>
       </c>
       <c r="R6" t="str">
-        <v/>
+        <v>O</v>
       </c>
       <c r="S6" t="str">
-        <v/>
+        <v>O</v>
       </c>
       <c r="T6" t="str">
         <v/>
@@ -1531,17 +1120,17 @@
       <c r="V6" t="str">
         <v/>
       </c>
-      <c r="W6" t="str">
-        <v/>
-      </c>
-      <c r="X6" t="str">
-        <v/>
+      <c r="W6">
+        <v>2</v>
+      </c>
+      <c r="X6">
+        <v>214</v>
       </c>
       <c r="Y6" t="str">
-        <v/>
-      </c>
-      <c r="Z6" t="str">
-        <v/>
+        <v>188|214</v>
+      </c>
+      <c r="Z6">
+        <v>4</v>
       </c>
       <c r="AA6" t="str">
         <v/>
@@ -1562,7 +1151,7 @@
         <v/>
       </c>
       <c r="AG6" t="str">
-        <v/>
+        <v>L=800 &gt; 600 mm → charnière center ; tiroirs 188 puis 214 mm</v>
       </c>
     </row>
     <row r="7">
@@ -1570,7 +1159,7 @@
         <v>O</v>
       </c>
       <c r="B7" t="str">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -1671,7 +1260,7 @@
         <v>O</v>
       </c>
       <c r="B8" t="str">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -1772,7 +1361,7 @@
         <v>O</v>
       </c>
       <c r="B9" t="str">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -1873,7 +1462,7 @@
         <v>O</v>
       </c>
       <c r="B10" t="str">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -1974,7 +1563,7 @@
         <v>O</v>
       </c>
       <c r="B11" t="str">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -2075,7 +1664,7 @@
         <v>O</v>
       </c>
       <c r="B12" t="str">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -2176,7 +1765,7 @@
         <v>O</v>
       </c>
       <c r="B13" t="str">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -2277,7 +1866,7 @@
         <v>O</v>
       </c>
       <c r="B14" t="str">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -2378,7 +1967,7 @@
         <v>O</v>
       </c>
       <c r="B15" t="str">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -2479,7 +2068,7 @@
         <v>O</v>
       </c>
       <c r="B16" t="str">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -2580,7 +2169,7 @@
         <v>O</v>
       </c>
       <c r="B17" t="str">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -2681,7 +2270,7 @@
         <v>O</v>
       </c>
       <c r="B18" t="str">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -2782,7 +2371,7 @@
         <v>O</v>
       </c>
       <c r="B19" t="str">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -2883,7 +2472,7 @@
         <v>O</v>
       </c>
       <c r="B20" t="str">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -2984,7 +2573,7 @@
         <v>O</v>
       </c>
       <c r="B21" t="str">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -3085,7 +2674,7 @@
         <v>O</v>
       </c>
       <c r="B22" t="str">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -3186,7 +2775,7 @@
         <v>O</v>
       </c>
       <c r="B23" t="str">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -3282,325 +2871,16 @@
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>O</v>
-      </c>
-      <c r="B24" t="str">
-        <v>220</v>
-      </c>
-      <c r="C24" t="str">
-        <v/>
-      </c>
-      <c r="D24" t="str">
-        <v/>
-      </c>
-      <c r="E24" t="str">
-        <v/>
-      </c>
-      <c r="F24" t="str">
-        <v/>
-      </c>
-      <c r="G24" t="str">
-        <v/>
-      </c>
-      <c r="H24" t="str">
-        <v/>
-      </c>
-      <c r="I24" t="str">
-        <v/>
-      </c>
-      <c r="J24" t="str">
-        <v/>
-      </c>
-      <c r="K24" t="str">
-        <v/>
-      </c>
-      <c r="L24" t="str">
-        <v/>
-      </c>
-      <c r="M24" t="str">
-        <v>brut</v>
-      </c>
-      <c r="N24" t="str">
-        <v>olive</v>
-      </c>
-      <c r="O24" t="str">
-        <v/>
-      </c>
-      <c r="P24" t="str">
-        <v/>
-      </c>
-      <c r="Q24" t="str">
-        <v/>
-      </c>
-      <c r="R24" t="str">
-        <v/>
-      </c>
-      <c r="S24" t="str">
-        <v/>
-      </c>
-      <c r="T24" t="str">
-        <v/>
-      </c>
-      <c r="U24" t="str">
-        <v/>
-      </c>
-      <c r="V24" t="str">
-        <v/>
-      </c>
-      <c r="W24" t="str">
-        <v/>
-      </c>
-      <c r="X24" t="str">
-        <v/>
-      </c>
-      <c r="Y24" t="str">
-        <v/>
-      </c>
-      <c r="Z24" t="str">
-        <v/>
-      </c>
-      <c r="AA24" t="str">
-        <v/>
-      </c>
-      <c r="AB24" t="str">
-        <v/>
-      </c>
-      <c r="AC24" t="str">
-        <v/>
-      </c>
-      <c r="AD24" t="str">
-        <v/>
-      </c>
-      <c r="AE24" t="str">
-        <v/>
-      </c>
-      <c r="AF24" t="str">
-        <v/>
-      </c>
-      <c r="AG24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>O</v>
-      </c>
-      <c r="B25" t="str">
-        <v>221</v>
-      </c>
-      <c r="C25" t="str">
-        <v/>
-      </c>
-      <c r="D25" t="str">
-        <v/>
-      </c>
-      <c r="E25" t="str">
-        <v/>
-      </c>
-      <c r="F25" t="str">
-        <v/>
-      </c>
-      <c r="G25" t="str">
-        <v/>
-      </c>
-      <c r="H25" t="str">
-        <v/>
-      </c>
-      <c r="I25" t="str">
-        <v/>
-      </c>
-      <c r="J25" t="str">
-        <v/>
-      </c>
-      <c r="K25" t="str">
-        <v/>
-      </c>
-      <c r="L25" t="str">
-        <v/>
-      </c>
-      <c r="M25" t="str">
-        <v>brut</v>
-      </c>
-      <c r="N25" t="str">
-        <v>olive</v>
-      </c>
-      <c r="O25" t="str">
-        <v/>
-      </c>
-      <c r="P25" t="str">
-        <v/>
-      </c>
-      <c r="Q25" t="str">
-        <v/>
-      </c>
-      <c r="R25" t="str">
-        <v/>
-      </c>
-      <c r="S25" t="str">
-        <v/>
-      </c>
-      <c r="T25" t="str">
-        <v/>
-      </c>
-      <c r="U25" t="str">
-        <v/>
-      </c>
-      <c r="V25" t="str">
-        <v/>
-      </c>
-      <c r="W25" t="str">
-        <v/>
-      </c>
-      <c r="X25" t="str">
-        <v/>
-      </c>
-      <c r="Y25" t="str">
-        <v/>
-      </c>
-      <c r="Z25" t="str">
-        <v/>
-      </c>
-      <c r="AA25" t="str">
-        <v/>
-      </c>
-      <c r="AB25" t="str">
-        <v/>
-      </c>
-      <c r="AC25" t="str">
-        <v/>
-      </c>
-      <c r="AD25" t="str">
-        <v/>
-      </c>
-      <c r="AE25" t="str">
-        <v/>
-      </c>
-      <c r="AF25" t="str">
-        <v/>
-      </c>
-      <c r="AG25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>O</v>
-      </c>
-      <c r="B26" t="str">
-        <v>222</v>
-      </c>
-      <c r="C26" t="str">
-        <v/>
-      </c>
-      <c r="D26" t="str">
-        <v/>
-      </c>
-      <c r="E26" t="str">
-        <v/>
-      </c>
-      <c r="F26" t="str">
-        <v/>
-      </c>
-      <c r="G26" t="str">
-        <v/>
-      </c>
-      <c r="H26" t="str">
-        <v/>
-      </c>
-      <c r="I26" t="str">
-        <v/>
-      </c>
-      <c r="J26" t="str">
-        <v/>
-      </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26" t="str">
-        <v/>
-      </c>
-      <c r="M26" t="str">
-        <v>brut</v>
-      </c>
-      <c r="N26" t="str">
-        <v>olive</v>
-      </c>
-      <c r="O26" t="str">
-        <v/>
-      </c>
-      <c r="P26" t="str">
-        <v/>
-      </c>
-      <c r="Q26" t="str">
-        <v/>
-      </c>
-      <c r="R26" t="str">
-        <v/>
-      </c>
-      <c r="S26" t="str">
-        <v/>
-      </c>
-      <c r="T26" t="str">
-        <v/>
-      </c>
-      <c r="U26" t="str">
-        <v/>
-      </c>
-      <c r="V26" t="str">
-        <v/>
-      </c>
-      <c r="W26" t="str">
-        <v/>
-      </c>
-      <c r="X26" t="str">
-        <v/>
-      </c>
-      <c r="Y26" t="str">
-        <v/>
-      </c>
-      <c r="Z26" t="str">
-        <v/>
-      </c>
-      <c r="AA26" t="str">
-        <v/>
-      </c>
-      <c r="AB26" t="str">
-        <v/>
-      </c>
-      <c r="AC26" t="str">
-        <v/>
-      </c>
-      <c r="AD26" t="str">
-        <v/>
-      </c>
-      <c r="AE26" t="str">
-        <v/>
-      </c>
-      <c r="AF26" t="str">
-        <v/>
-      </c>
-      <c r="AG26" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AG26"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AG26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AG23"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C27"/>
-  <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="42.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:C13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3615,46 +2895,46 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Boutique</v>
+        <v>couleur_ossature</v>
       </c>
       <c r="B2" t="str">
-        <v>O</v>
+        <v>brut</v>
       </c>
       <c r="C2" t="str">
-        <v>Visible en boutique</v>
+        <v>Brut</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Boutique</v>
+        <v>couleur_ossature</v>
       </c>
       <c r="B3" t="str">
-        <v>(vide)</v>
+        <v>vernis_clair</v>
       </c>
       <c r="C3" t="str">
-        <v>Masqué</v>
+        <v>Vernis</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>couleur_ossature</v>
+        <v>couleur_panneau</v>
       </c>
       <c r="B4" t="str">
-        <v>brut</v>
+        <v>terracotta</v>
       </c>
       <c r="C4" t="str">
-        <v>Brut</v>
+        <v>Terracotta</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>couleur_ossature</v>
+        <v>couleur_panneau</v>
       </c>
       <c r="B5" t="str">
-        <v>vernis_clair</v>
+        <v>olive</v>
       </c>
       <c r="C5" t="str">
-        <v>Vernis</v>
+        <v>Olive</v>
       </c>
     </row>
     <row r="6">
@@ -3662,10 +2942,10 @@
         <v>couleur_panneau</v>
       </c>
       <c r="B6" t="str">
-        <v>terracotta</v>
+        <v>bleu_poudre</v>
       </c>
       <c r="C6" t="str">
-        <v>Terracotta</v>
+        <v>Bleu clair poudré</v>
       </c>
     </row>
     <row r="7">
@@ -3673,10 +2953,10 @@
         <v>couleur_panneau</v>
       </c>
       <c r="B7" t="str">
-        <v>olive</v>
+        <v>gris_cendre</v>
       </c>
       <c r="C7" t="str">
-        <v>Olive</v>
+        <v>Gris cendre blanc</v>
       </c>
     </row>
     <row r="8">
@@ -3684,10 +2964,10 @@
         <v>couleur_panneau</v>
       </c>
       <c r="B8" t="str">
-        <v>bleu_poudre</v>
+        <v>jaune_orange</v>
       </c>
       <c r="C8" t="str">
-        <v>Bleu clair poudré</v>
+        <v>Jaune orangé clair</v>
       </c>
     </row>
     <row r="9">
@@ -3695,32 +2975,32 @@
         <v>couleur_panneau</v>
       </c>
       <c r="B9" t="str">
-        <v>gris_cendre</v>
+        <v>noir_mat</v>
       </c>
       <c r="C9" t="str">
-        <v>Gris cendre blanc</v>
+        <v>Noir mat</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>couleur_panneau</v>
+        <v>porte_charniere</v>
       </c>
       <c r="B10" t="str">
-        <v>jaune_orange</v>
+        <v>left</v>
       </c>
       <c r="C10" t="str">
-        <v>Jaune orangé clair</v>
+        <v>Battant gauche</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>couleur_panneau</v>
+        <v>porte_charniere</v>
       </c>
       <c r="B11" t="str">
-        <v>noir_mat</v>
+        <v>right</v>
       </c>
       <c r="C11" t="str">
-        <v>Noir mat</v>
+        <v>Battant droit</v>
       </c>
     </row>
     <row r="12">
@@ -3728,180 +3008,26 @@
         <v>porte_charniere</v>
       </c>
       <c r="B12" t="str">
-        <v>left</v>
+        <v>center</v>
       </c>
       <c r="C12" t="str">
-        <v>Battant gauche</v>
+        <v>Double / milieu (si L &gt; 600)</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>porte_charniere</v>
+        <v>hauteur_tiroir</v>
       </c>
       <c r="B13" t="str">
-        <v>right</v>
+        <v>58 / 84 / 110 / 136 / 162 / 188 / 214 / 240 / 266</v>
       </c>
       <c r="C13" t="str">
-        <v>Battant droit</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>porte_charniere</v>
-      </c>
-      <c r="B14" t="str">
-        <v>center</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Double / milieu (obligatoire si L &gt; 600)</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>panneau O/N</v>
-      </c>
-      <c r="B15" t="str">
-        <v>O</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Présent</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>panneau O/N</v>
-      </c>
-      <c r="B16" t="str">
-        <v>(vide)</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Absent</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>hauteur_tiroir</v>
-      </c>
-      <c r="B17">
-        <v>58</v>
-      </c>
-      <c r="C17" t="str">
-        <v>Würth</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>hauteur_tiroir</v>
-      </c>
-      <c r="B18">
-        <v>84</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Würth</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>hauteur_tiroir</v>
-      </c>
-      <c r="B19">
-        <v>110</v>
-      </c>
-      <c r="C19" t="str">
-        <v>Würth (défaut)</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>hauteur_tiroir</v>
-      </c>
-      <c r="B20">
-        <v>136</v>
-      </c>
-      <c r="C20" t="str">
-        <v>Würth</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>hauteur_tiroir</v>
-      </c>
-      <c r="B21">
-        <v>162</v>
-      </c>
-      <c r="C21" t="str">
-        <v>Würth</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>hauteur_tiroir</v>
-      </c>
-      <c r="B22">
-        <v>188</v>
-      </c>
-      <c r="C22" t="str">
-        <v>Würth</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>hauteur_tiroir</v>
-      </c>
-      <c r="B23">
-        <v>214</v>
-      </c>
-      <c r="C23" t="str">
-        <v>Würth</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>hauteur_tiroir</v>
-      </c>
-      <c r="B24">
-        <v>240</v>
-      </c>
-      <c r="C24" t="str">
-        <v>Würth</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>hauteur_tiroir</v>
-      </c>
-      <c r="B25">
-        <v>266</v>
-      </c>
-      <c r="C25" t="str">
-        <v>Würth</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>L P H</v>
-      </c>
-      <c r="B26">
-        <v>200</v>
-      </c>
-      <c r="C26" t="str">
-        <v>minimum mm</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>L P H</v>
-      </c>
-      <c r="B27">
-        <v>2200</v>
-      </c>
-      <c r="C27" t="str">
-        <v>maximum mm</v>
+        <v>Würth ASTUCIO B</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>